--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_13_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_13_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7947</v>
+        <v>4.8439</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8739</v>
+        <v>2.2592</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9208</v>
+        <v>2.5847</v>
       </c>
       <c r="G2" t="n">
         <v>2.2105</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5816</v>
+        <v>0.6308</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1845</v>
+        <v>0.2008</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7662</v>
+        <v>0.4301</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1511</v>
+        <v>4.6886</v>
       </c>
       <c r="E3" t="n">
-        <v>3.997</v>
+        <v>4.7362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.154</v>
+        <v>-0.0476</v>
       </c>
       <c r="G3" t="n">
         <v>3.9896</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9287</v>
+        <v>-0.3912</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8883</v>
+        <v>-0.1491</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0404</v>
+        <v>-0.242</v>
       </c>
       <c r="V3" t="n">
         <v>0.3943</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8472</v>
+        <v>3.2424</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0841</v>
+        <v>0.4231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.763</v>
+        <v>2.8193</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0995</v>
+        <v>0.8813</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5943</v>
+        <v>1.2594</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5052</v>
+        <v>-0.3781</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8205</v>
+        <v>-0.1197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.2017</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9802999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2789</v>
+        <v>1.001</v>
       </c>
       <c r="N4" t="n">
-        <v>0.754</v>
+        <v>1.0578</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4751</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2838</v>
+        <v>0.8766</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2636</v>
+        <v>0.5427</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0202</v>
+        <v>0.3339</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7541</v>
+        <v>3.1237</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0692</v>
+        <v>1.7229</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6849</v>
+        <v>1.4008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8813</v>
+        <v>2.2443</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2594</v>
+        <v>3.4824</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3781</v>
+        <v>-1.2382</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1197</v>
+        <v>0.6465</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2017</v>
+        <v>2.457</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3213</v>
+        <v>-1.8105</v>
       </c>
       <c r="M5" t="n">
-        <v>1.001</v>
+        <v>1.5977</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0578</v>
+        <v>1.0254</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0568</v>
+        <v>0.5723</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3883</v>
+        <v>-0.0483</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1889</v>
+        <v>0.0042</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1994</v>
+        <v>-0.0525</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9135</v>
+        <v>2.5948</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7479</v>
+        <v>1.9662</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1656</v>
+        <v>0.6286</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2443</v>
+        <v>2.0995</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4824</v>
+        <v>1.5943</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2382</v>
+        <v>0.5052</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6465</v>
+        <v>1.8205</v>
       </c>
       <c r="K6" t="n">
-        <v>2.457</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8105</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5977</v>
+        <v>0.2789</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0254</v>
+        <v>0.754</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5723</v>
+        <v>-0.4751</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2586</v>
+        <v>0.0314</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9709</v>
+        <v>0.1456</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2877</v>
+        <v>-0.1142</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2804</v>
+        <v>0.6872</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2453</v>
+        <v>-0.3946</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9649</v>
+        <v>1.0818</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5248</v>
+        <v>0.6214</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3986</v>
+        <v>-1.132</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9234</v>
+        <v>1.7533</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.425</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6421</v>
+        <v>-0.7527</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184</v>
+        <v>1.1778</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3509</v>
+        <v>0.1963</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2435</v>
+        <v>-0.3792</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1074</v>
+        <v>0.5756</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2744</v>
+        <v>-0.7538</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3882</v>
+        <v>-0.4795</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1138</v>
+        <v>-0.2743</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3247</v>
+        <v>0.8197</v>
       </c>
       <c r="W7" t="n">
-        <v>0.031</v>
+        <v>0.8197</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518</v>
+        <v>0.2764</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6619</v>
+        <v>1.1405</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9137</v>
+        <v>-0.864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6214</v>
+        <v>-0.5248</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.132</v>
+        <v>0.3986</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7533</v>
+        <v>-0.9234</v>
       </c>
       <c r="J8" t="n">
-        <v>0.425</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7527</v>
+        <v>0.6421</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1778</v>
+        <v>0.184</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1963</v>
+        <v>-1.3509</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-0.2435</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5756</v>
+        <v>-1.1074</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1892</v>
+        <v>0.2704</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>0.2833</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4424</v>
+        <v>-0.013</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8197</v>
+        <v>-1.3247</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8197</v>
+        <v>0.031</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5057</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3785</v>
+        <v>-1.3471</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8842</v>
+        <v>0.5191</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.6407</v>
+        <v>1.0797</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6507</v>
+        <v>0.0625</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01</v>
+        <v>1.0172</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2287</v>
+        <v>-0.1246</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7674</v>
+        <v>-0.1982</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5386</v>
+        <v>0.0736</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.412</v>
+        <v>1.2042</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8834</v>
+        <v>0.2606</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5286</v>
+        <v>0.9436</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4391</v>
+        <v>-0.3716</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6948</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2557</v>
+        <v>-0.3088</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2805</v>
+        <v>-1.0183</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7324</v>
+        <v>0.5535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4519</v>
+        <v>-1.5718</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0797</v>
+        <v>0.8284</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0625</v>
+        <v>-1.0888</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0172</v>
+        <v>1.9172</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1246</v>
+        <v>1.6935</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1982</v>
+        <v>-0.6988</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0736</v>
+        <v>2.3923</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2042</v>
+        <v>-0.8651</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2606</v>
+        <v>-0.39</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9436</v>
+        <v>-0.4751</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.5425</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4481</v>
+        <v>0.0198</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.376</v>
+        <v>-0.5623</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4633</v>
+        <v>-1.0559</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2429</v>
+        <v>-0.8563</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7062</v>
+        <v>-0.1996</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8284</v>
+        <v>-1.0866</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0888</v>
+        <v>-1.0432</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9172</v>
+        <v>-0.0435</v>
       </c>
       <c r="J11" t="n">
-        <v>1.6935</v>
+        <v>-0.8793</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6988</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3923</v>
+        <v>-0.2477</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8651</v>
+        <v>-0.2073</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.39</v>
+        <v>-0.4116</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4751</v>
+        <v>0.2042</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9875</v>
+        <v>0.0334</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2908</v>
+        <v>-0.0312</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6967</v>
+        <v>0.0646</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8457</v>
+        <v>-1.7285</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7134</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1324</v>
+        <v>-0.8842</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.0866</v>
+        <v>-2.6407</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0432</v>
+        <v>-2.6507</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0435</v>
+        <v>0.01</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8793</v>
+        <v>-1.2287</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-1.7674</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2477</v>
+        <v>0.5386</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2073</v>
+        <v>-1.412</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4116</v>
+        <v>-0.8834</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2042</v>
+        <v>-0.5286</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7565</v>
+        <v>0.2164</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8883</v>
+        <v>0.472</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1318</v>
+        <v>-0.2557</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8764</v>
+        <v>-2.6849</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9707</v>
+        <v>-2.6784</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09429999999999999</v>
+        <v>-0.0065</v>
       </c>
       <c r="G13" t="n">
         <v>0.4844</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5643</v>
+        <v>0.7558</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3566</v>
+        <v>0.6488</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6778999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.0212</v>
+        <v>12.1413</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5604</v>
+        <v>6.680900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>5.4605</v>
+        <v>5.460600000000002</v>
       </c>
       <c r="G14" t="n">
         <v>10.187</v>
@@ -1516,19 +1516,19 @@
         <v>2.5747</v>
       </c>
       <c r="I14" t="n">
-        <v>7.612</v>
+        <v>7.612000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>9.258000000000001</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8645</v>
+        <v>1.864499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.393599999999999</v>
+        <v>7.3936</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9285999999999999</v>
+        <v>0.9286000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0.7101</v>
@@ -1546,13 +1546,13 @@
         <v>13.9173</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4131</v>
+        <v>0.7074</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4744000000000003</v>
+        <v>1.5946</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8873</v>
+        <v>-0.8872</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1561,13 +1561,13 @@
         <v>7.425700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.498000000000001</v>
+        <v>-8.497999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8651</v>
+        <v>2.0269</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2369</v>
+        <v>3.6269</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3718</v>
+        <v>-1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2918</v>
+        <v>0.9233</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1751</v>
+        <v>-1.8102</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8833</v>
+        <v>2.7335</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6847</v>
+        <v>3.0754</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8822</v>
+        <v>-0.6617</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1975</v>
+        <v>3.7371</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3929</v>
+        <v>-2.1521</v>
       </c>
       <c r="N15" t="n">
-        <v>0.293</v>
+        <v>-1.1484</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6859</v>
+        <v>-1.0037</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5759</v>
+        <v>-0.2702</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3383</v>
+        <v>-0.0389</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2377</v>
+        <v>-0.2313</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>1.7501</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9142</v>
+        <v>1.4612</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2791</v>
+        <v>3.001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.635</v>
+        <v>-1.5398</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.1625</v>
+        <v>1.2918</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.0072</v>
+        <v>2.1751</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.1553</v>
+        <v>-0.8833</v>
       </c>
       <c r="J16" t="n">
-        <v>-4.8212</v>
+        <v>1.6847</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.0376</v>
+        <v>1.8822</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.7836</v>
+        <v>-0.1975</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3413</v>
+        <v>-0.3929</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9696</v>
+        <v>0.293</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3717</v>
+        <v>-0.6859</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2158</v>
+        <v>0.172</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8837</v>
+        <v>0.1024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3321</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>4.0052</v>
+        <v>-0.9304</v>
       </c>
       <c r="W16" t="n">
-        <v>3.2166</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7886</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8885</v>
+        <v>0.274</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0201</v>
+        <v>0.4026</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8683999999999999</v>
+        <v>-0.1286</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1623</v>
+        <v>1.0229</v>
       </c>
       <c r="H17" t="n">
-        <v>0.982</v>
+        <v>0.7083</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8196</v>
+        <v>0.3145</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3169</v>
+        <v>0.2689</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1329</v>
+        <v>0.2689</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1546</v>
+        <v>0.754</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1509</v>
+        <v>0.4395</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0037</v>
+        <v>0.3145</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3498</v>
+        <v>0.0914</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1824</v>
+        <v>0.1338</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1674</v>
+        <v>-0.0424</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5943000000000001</v>
+        <v>-0.4362</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7565</v>
+        <v>-1.1594</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1622</v>
+        <v>0.7232</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0229</v>
+        <v>0.1623</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7083</v>
+        <v>0.982</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3145</v>
+        <v>-0.8196</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2689</v>
+        <v>1.3169</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2689</v>
+        <v>1.1329</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.184</v>
       </c>
       <c r="M18" t="n">
-        <v>0.754</v>
+        <v>-1.1546</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4395</v>
+        <v>-0.1509</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>-1.0037</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4116</v>
+        <v>1.0251</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4876</v>
+        <v>1.0029</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.076</v>
+        <v>0.0222</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2697</v>
+        <v>-0.5343</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3294</v>
+        <v>-1.8638</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0597</v>
+        <v>1.3295</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9233</v>
+        <v>1.1448</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8102</v>
+        <v>0.76</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7335</v>
+        <v>0.3848</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0754</v>
+        <v>0.5837</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6617</v>
+        <v>0.3529</v>
       </c>
       <c r="L19" t="n">
-        <v>3.7371</v>
+        <v>0.2308</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1521</v>
+        <v>0.5611</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1484</v>
+        <v>0.4071</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0037</v>
+        <v>0.154</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0274</v>
+        <v>-0.4266</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3364</v>
+        <v>-0.4991</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6909999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.7886</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7501</v>
+        <v>-0.7886</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2078</v>
+        <v>-0.6293</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3356</v>
+        <v>-1.0183</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1278</v>
+        <v>0.389</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1448</v>
+        <v>-7.1625</v>
       </c>
       <c r="H20" t="n">
-        <v>0.76</v>
+        <v>-4.0072</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3848</v>
+        <v>-3.1553</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5837</v>
+        <v>-4.8212</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3529</v>
+        <v>-3.0376</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2308</v>
+        <v>-1.7836</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5611</v>
+        <v>-2.3413</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4071</v>
+        <v>-0.9696</v>
       </c>
       <c r="O20" t="n">
-        <v>0.154</v>
+        <v>-1.3717</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1</v>
+        <v>0.6723</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1291</v>
+        <v>0.0861</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7886</v>
+        <v>4.0052</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7886</v>
+        <v>3.2166</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2307</v>
+        <v>-1.0394</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3372</v>
+        <v>0.2221</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5679</v>
+        <v>-1.2616</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9882</v>
+        <v>-2.2095</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.851</v>
+        <v>-0.2388</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1372</v>
+        <v>-1.9708</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0736</v>
+        <v>-1.0155</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.3732</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-1.3887</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0618</v>
+        <v>-1.1941</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.851</v>
+        <v>-0.612</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2108</v>
+        <v>-0.5821</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2034</v>
+        <v>0.0619</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>0.1654</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0602</v>
+        <v>-0.1034</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2836</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2881</v>
+        <v>-1.2038</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3877</v>
+        <v>-0.2697</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9004</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0.8325</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0444</v>
+        <v>0.1287</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3969</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5499</v>
+        <v>-1.6689</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1042</v>
+        <v>-0.1346</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6541</v>
+        <v>-1.5343</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2095</v>
+        <v>-0.9882</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2388</v>
+        <v>-0.851</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9708</v>
+        <v>-0.1372</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0155</v>
+        <v>0.0736</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3732</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3887</v>
+        <v>0.0736</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1941</v>
+        <v>-1.0618</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.612</v>
+        <v>-0.851</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5821</v>
+        <v>-0.2108</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4485</v>
+        <v>-0.2348</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0474</v>
+        <v>-0.2082</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.496</v>
+        <v>-0.0266</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2836</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3558</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0145</v>
+        <v>-3.1723</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8272</v>
+        <v>-3.1195</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1873</v>
+        <v>-0.0529</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2666</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1448</v>
+        <v>-0.3027</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9709</v>
+        <v>-0.2631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.174</v>
+        <v>-0.0395</v>
       </c>
       <c r="V24" t="n">
         <v>0.7886</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.262</v>
+        <v>-5.3126</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9736</v>
+        <v>-5.1479</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2884</v>
+        <v>-0.1647</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9377</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6673</v>
+        <v>0.282</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8136</v>
+        <v>0.0121</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1463</v>
+        <v>0.27</v>
       </c>
       <c r="V25" t="n">
         <v>1.7501</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.0212</v>
+        <v>-10.2347</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.460699999999999</v>
+        <v>-5.460599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.560599999999999</v>
+        <v>-4.7742</v>
       </c>
       <c r="G26" t="n">
         <v>-10.1869</v>
@@ -2455,13 +2455,13 @@
         <v>-7.6122</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9287999999999996</v>
+        <v>-0.9287999999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7100999999999998</v>
+        <v>-0.7101</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2187000000000008</v>
+        <v>-0.2186999999999998</v>
       </c>
       <c r="M26" t="n">
         <v>-9.258199999999999</v>
@@ -2470,7 +2470,7 @@
         <v>-1.8642</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.393799999999999</v>
+        <v>-7.393800000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-2.3194</v>
@@ -2482,19 +2482,19 @@
         <v>11.5977</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4129</v>
+        <v>1.1991</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8871999999999997</v>
+        <v>0.8873999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4743999999999998</v>
+        <v>0.3120000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0722</v>
+        <v>1.072200000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>8.498000000000001</v>
+        <v>8.497999999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-7.425800000000001</v>
